--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488119_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488119_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.349</v>
+        <v>10.0258</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8897</v>
+        <v>7.2577</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4593</v>
+        <v>2.7682</v>
       </c>
       <c r="G2" t="n">
         <v>8.9269</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.598</v>
+        <v>0.0789</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1176</v>
+        <v>0.4856</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7156</v>
+        <v>-0.4067</v>
       </c>
       <c r="V2" t="n">
         <v>0.6237</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9471</v>
+        <v>6.155</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9653</v>
+        <v>3.3978</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9818</v>
+        <v>2.7572</v>
       </c>
       <c r="G3" t="n">
         <v>2.3484</v>
@@ -688,13 +688,13 @@
         <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>3.22</v>
+        <v>1.4279</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6689</v>
+        <v>1.1014</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5511</v>
+        <v>0.3265</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6069</v>
+        <v>5.1849</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5756</v>
+        <v>3.4618</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0313</v>
+        <v>1.7231</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5603</v>
+        <v>2.1471</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4754</v>
+        <v>3.1246</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0849</v>
+        <v>-0.9775</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0035</v>
+        <v>2.233</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3317</v>
+        <v>2.2939</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6717</v>
+        <v>-0.0609</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5569</v>
+        <v>-0.0859</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1437</v>
+        <v>0.8307</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4132</v>
+        <v>-0.9166</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0221</v>
+        <v>0.3588</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4368</v>
+        <v>0.213</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4147</v>
+        <v>0.1457</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3278</v>
+        <v>1.8861</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3278</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2085</v>
+        <v>5.1786</v>
       </c>
       <c r="E5" t="n">
-        <v>3.808</v>
+        <v>4.1473</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4004</v>
+        <v>1.0313</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4614</v>
+        <v>5.5603</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1172</v>
+        <v>1.4754</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3442</v>
+        <v>4.0849</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2792</v>
+        <v>5.0035</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9578</v>
+        <v>1.3317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3214</v>
+        <v>3.6717</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1822</v>
+        <v>0.5569</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1594</v>
+        <v>0.1437</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0228</v>
+        <v>0.4132</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6873</v>
+        <v>0.5497</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9164</v>
+        <v>0.135</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7709</v>
+        <v>0.4147</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9314</v>
+        <v>-1.3278</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.5349</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1172</v>
+        <v>4.2555</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6468</v>
+        <v>2.2843</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4704</v>
+        <v>1.9712</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1471</v>
+        <v>3.2539</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1246</v>
+        <v>2.1157</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9775</v>
+        <v>1.1382</v>
       </c>
       <c r="J6" t="n">
-        <v>2.233</v>
+        <v>3.1376</v>
       </c>
       <c r="K6" t="n">
         <v>2.2939</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0609</v>
+        <v>0.8437</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0859</v>
+        <v>0.1162</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8307</v>
+        <v>-0.1782</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9166</v>
+        <v>0.2945</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R6" t="n">
-        <v>1.784</v>
+        <v>2.3787</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7089</v>
+        <v>0.0522</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6019</v>
+        <v>0.3094</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.107</v>
+        <v>-0.2572</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8861</v>
+        <v>1.5441</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0068</v>
+        <v>1.8107</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1207</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.8875</v>
+        <v>3.6743</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9163</v>
+        <v>0.7244</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9712</v>
+        <v>2.9499</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2539</v>
+        <v>3.7647</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1157</v>
+        <v>3.1354</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1382</v>
+        <v>0.6294</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1376</v>
+        <v>3.0585</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2939</v>
+        <v>3.2555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8437</v>
+        <v>-0.197</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1162</v>
+        <v>0.7062</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1782</v>
+        <v>-0.1201</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2945</v>
+        <v>0.8264</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5947</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3787</v>
+        <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3158</v>
+        <v>0.4358</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0586</v>
+        <v>0.3727</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2572</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5441</v>
+        <v>0.2666</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8107</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8665</v>
+        <v>2.3507</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1132</v>
+        <v>2.4837</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7533</v>
+        <v>-0.1331</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7647</v>
+        <v>2.4614</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1354</v>
+        <v>2.1172</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6294</v>
+        <v>0.3442</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0585</v>
+        <v>2.2792</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2555</v>
+        <v>1.9578</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.197</v>
+        <v>0.3214</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7062</v>
+        <v>0.1822</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1201</v>
+        <v>0.1594</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8264</v>
+        <v>0.0228</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3719</v>
+        <v>0.8295</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2386</v>
+        <v>0.5921</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1334</v>
+        <v>0.2374</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2666</v>
+        <v>-1.9314</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.5349</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7973</v>
+        <v>1.2548</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5494</v>
+        <v>-2.1305</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3467</v>
+        <v>3.3853</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9036999999999999</v>
+        <v>-0.5313</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2786</v>
+        <v>-1.7672</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1823</v>
+        <v>1.2359</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4577</v>
+        <v>-1.6393</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4301</v>
+        <v>-2.3262</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8878</v>
+        <v>0.6869</v>
       </c>
       <c r="M10" t="n">
-        <v>0.446</v>
+        <v>1.108</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1515</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2945</v>
+        <v>0.549</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5769</v>
+        <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5258</v>
+        <v>0.3716</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9949</v>
+        <v>-0.1036</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5309</v>
+        <v>0.4752</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.218</v>
+        <v>0.8198</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.0109</v>
+        <v>0.6036</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2071</v>
+        <v>0.2163</v>
       </c>
     </row>
     <row r="11">
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9053</v>
+        <v>1.1266</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9053</v>
+        <v>-0.855</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.9817</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9053</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3027</v>
+        <v>-0.2786</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6027</v>
+        <v>1.1823</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9053</v>
+        <v>0.4577</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3027</v>
+        <v>-0.4301</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6027</v>
+        <v>0.8878</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.446</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.1515</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2945</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.8552</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.6893</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.218</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-1.0109</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6269</v>
+        <v>0.9053</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7022</v>
+        <v>0.9053</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3291</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5313</v>
+        <v>0.9053</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7672</v>
+        <v>0.3027</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2359</v>
+        <v>0.6027</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6393</v>
+        <v>0.9053</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.3262</v>
+        <v>0.3027</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6869</v>
+        <v>0.6027</v>
       </c>
       <c r="M13" t="n">
-        <v>1.108</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.549</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2563</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6753</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4191</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8198</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1371</v>
+        <v>-1.6245</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.3803</v>
+        <v>-3.1765</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2431</v>
+        <v>1.552</v>
       </c>
       <c r="G15" t="n">
         <v>0.4189</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1685</v>
+        <v>0.3441</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0038</v>
+        <v>0.2075</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1723</v>
+        <v>0.1366</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6036</v>
@@ -1657,16 +1657,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>43.00449999999999</v>
+        <v>43.31640000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>23.0177</v>
+        <v>23.3297</v>
       </c>
       <c r="F16" t="n">
-        <v>19.9866</v>
+        <v>19.9868</v>
       </c>
       <c r="G16" t="n">
-        <v>34.98869999999999</v>
+        <v>34.9887</v>
       </c>
       <c r="H16" t="n">
         <v>15.522</v>
@@ -1681,7 +1681,7 @@
         <v>13.308</v>
       </c>
       <c r="L16" t="n">
-        <v>18.588</v>
+        <v>18.58799999999999</v>
       </c>
       <c r="M16" t="n">
         <v>3.0928</v>
@@ -1690,10 +1690,10 @@
         <v>2.2141</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8787000000000001</v>
+        <v>0.8786999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9644</v>
+        <v>3.964399999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>-16.8488</v>
@@ -1702,16 +1702,16 @@
         <v>20.8136</v>
       </c>
       <c r="S16" t="n">
-        <v>4.9916</v>
+        <v>5.3037</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6904</v>
+        <v>4.0024</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3012</v>
+        <v>1.3013</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9404999999999999</v>
+        <v>-0.9405</v>
       </c>
       <c r="W16" t="n">
         <v>4.2804</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1056</v>
+        <v>0.7377</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1479</v>
+        <v>0.2596</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2535</v>
+        <v>0.4781</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0534</v>
@@ -1780,13 +1780,13 @@
         <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2047</v>
+        <v>-0.5726</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0497</v>
+        <v>-0.6422</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.155</v>
+        <v>0.0696</v>
       </c>
       <c r="V17" t="n">
         <v>3.3547</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4444</v>
+        <v>-1.6106</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4892</v>
+        <v>-0.7332</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9336</v>
+        <v>-0.8774</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2182</v>
@@ -1858,13 +1858,13 @@
         <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5757</v>
+        <v>0.4094</v>
       </c>
       <c r="T18" t="n">
-        <v>1.843</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2673</v>
+        <v>-0.2112</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.418</v>
+        <v>-1.815</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2379</v>
+        <v>-0.7473</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1801</v>
+        <v>-1.0678</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0973</v>
@@ -1936,13 +1936,13 @@
         <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8092</v>
+        <v>0.4121</v>
       </c>
       <c r="T19" t="n">
-        <v>0.727</v>
+        <v>0.2177</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.1944</v>
       </c>
       <c r="V19" t="n">
         <v>0.2666</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0775</v>
+        <v>-2.5975</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2624</v>
+        <v>-1.1545</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1849</v>
+        <v>-1.443</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9448</v>
+        <v>-2.6012</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7151</v>
+        <v>-1.3977</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2297</v>
+        <v>-1.2035</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2407</v>
+        <v>0.1274</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9276</v>
+        <v>0.0069</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6869</v>
+        <v>0.1205</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7041</v>
+        <v>-2.7286</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7875</v>
+        <v>-1.4046</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9166</v>
+        <v>-1.3241</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4114</v>
+        <v>-0.591</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6936</v>
+        <v>-0.2908</v>
       </c>
       <c r="U20" t="n">
-        <v>1.105</v>
+        <v>-0.3002</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0076</v>
+        <v>-2.6327</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2572</v>
+        <v>-0.8497</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7504</v>
+        <v>-1.7831</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1389</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1879</v>
+        <v>-0.8131</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3727</v>
+        <v>-0.9653</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1848</v>
+        <v>0.1522</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2666</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1258</v>
+        <v>-2.6541</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6638</v>
+        <v>-2.1605</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.462</v>
+        <v>-0.4935</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6012</v>
+        <v>-1.9448</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3977</v>
+        <v>-1.7151</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2035</v>
+        <v>-0.2297</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1274</v>
+        <v>-0.2407</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0069</v>
+        <v>-0.9276</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1205</v>
+        <v>0.6869</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7286</v>
+        <v>-1.7041</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4046</v>
+        <v>-0.7875</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3241</v>
+        <v>-0.9166</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1193</v>
+        <v>-0.1652</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8001</v>
+        <v>-0.5917</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3191</v>
+        <v>0.4265</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5984</v>
+        <v>-3.1394</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0975</v>
+        <v>-1.69</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5009</v>
+        <v>-1.4494</v>
       </c>
       <c r="G23" t="n">
         <v>-1.69</v>
@@ -2248,13 +2248,13 @@
         <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0451</v>
+        <v>0.4139</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3782</v>
+        <v>0.7857</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4233</v>
+        <v>-0.3717</v>
       </c>
       <c r="V23" t="n">
         <v>-0.674</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7387</v>
+        <v>-4.1324</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5465</v>
+        <v>-3.3614</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1922</v>
+        <v>-0.771</v>
       </c>
       <c r="G24" t="n">
         <v>-5.5865</v>
@@ -2326,13 +2326,13 @@
         <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4425</v>
+        <v>0.0487</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9142</v>
+        <v>0.0993</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4718</v>
+        <v>-0.0506</v>
       </c>
       <c r="V24" t="n">
         <v>1.2071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1512</v>
+        <v>-4.2753</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2619</v>
+        <v>-2.4656</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8893</v>
+        <v>-1.8097</v>
       </c>
       <c r="G25" t="n">
         <v>-5.3876</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1512</v>
+        <v>-0.2753</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2534</v>
+        <v>0.0496</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4046</v>
+        <v>-0.3249</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. ZEA GONZALEZ</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.2902</v>
+        <v>-4.3048</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5147</v>
+        <v>0.2516</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.7755</v>
+        <v>-4.5564</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9096</v>
+        <v>-0.6698</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1599</v>
+        <v>-0.4518</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0695</v>
+        <v>-0.218</v>
       </c>
       <c r="J26" t="n">
-        <v>1.0291</v>
+        <v>4.0617</v>
       </c>
       <c r="K26" t="n">
-        <v>1.0291</v>
+        <v>1.756</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.3057</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.9386</v>
+        <v>-4.7315</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.8691</v>
+        <v>-2.2078</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.0695</v>
+        <v>-2.5237</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1893</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.9822</v>
+        <v>-4.9556</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7771</v>
+        <v>-1.6022</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5616</v>
+        <v>-0.6652</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2155</v>
+        <v>-0.9371</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.4142</v>
+        <v>0.9405</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.4142</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>M. ZEA GONZALEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.3385</v>
+        <v>-4.6966</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2577</v>
+        <v>-1.0054</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.0808</v>
+        <v>-3.6912</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6698</v>
+        <v>-0.9096</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4518</v>
+        <v>0.1599</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.218</v>
+        <v>-1.0695</v>
       </c>
       <c r="J27" t="n">
-        <v>4.0617</v>
+        <v>1.0291</v>
       </c>
       <c r="K27" t="n">
-        <v>1.756</v>
+        <v>1.0291</v>
       </c>
       <c r="L27" t="n">
-        <v>2.3057</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.7315</v>
+        <v>-1.9386</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.2078</v>
+        <v>-0.8691</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.5237</v>
+        <v>-1.0695</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.9733</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.9556</v>
+        <v>-1.9822</v>
       </c>
       <c r="R27" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.636</v>
+        <v>-0.1835</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.1745</v>
+        <v>-0.0522</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.4614</v>
+        <v>-0.1313</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9405</v>
+        <v>-2.4142</v>
       </c>
       <c r="W27" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.8701</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-10.9196</v>
+        <v>-10.5252</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.2284</v>
+        <v>-6.3303</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.6912</v>
+        <v>-4.195</v>
       </c>
       <c r="G28" t="n">
         <v>-7.6915</v>
@@ -2638,13 +2638,13 @@
         <v>1.3876</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.1092</v>
+        <v>-0.7148</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2351</v>
+        <v>0.1332</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.3443</v>
+        <v>-0.8481</v>
       </c>
       <c r="V28" t="n">
         <v>-0.5331</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-43.0043</v>
+        <v>-41.6459</v>
       </c>
       <c r="E29" t="n">
         <v>-19.9867</v>
       </c>
       <c r="F29" t="n">
-        <v>-23.0176</v>
+        <v>-21.6594</v>
       </c>
       <c r="G29" t="n">
         <v>-34.9888</v>
@@ -2695,7 +2695,7 @@
         <v>-2.213900000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.8787000000000007</v>
+        <v>-0.8787000000000003</v>
       </c>
       <c r="M29" t="n">
         <v>-31.896</v>
@@ -2710,19 +2710,19 @@
         <v>-3.9643</v>
       </c>
       <c r="Q29" t="n">
-        <v>-20.8132</v>
+        <v>-20.81319999999999</v>
       </c>
       <c r="R29" t="n">
         <v>16.849</v>
       </c>
       <c r="S29" t="n">
-        <v>-4.9917</v>
+        <v>-3.6336</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.3013</v>
+        <v>-1.3014</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.6904</v>
+        <v>-2.3324</v>
       </c>
       <c r="V29" t="n">
         <v>0.9404999999999998</v>
